--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135615652</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135615634</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135615637</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135615643</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135615653</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135615659</v>
       </c>
       <c r="B7" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135615625</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135615626</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135615627</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135615628</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135615629</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135615636</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135615641</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135615642</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135615644</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135615646</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135615649</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135615658</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135615660</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135615664</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135615665</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135615666</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135615667</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135615670</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135615671</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135615672</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135615674</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135615675</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135615631</v>
       </c>
       <c r="B31" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135615640</v>
       </c>
       <c r="B32" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135615663</v>
       </c>
       <c r="B33" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135615632</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135615635</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135615639</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135615645</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135615647</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135615648</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135615654</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135615656</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135615657</v>
       </c>
       <c r="B42" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135615661</v>
       </c>
       <c r="B43" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135615662</v>
       </c>
       <c r="B44" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135615668</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135615673</v>
       </c>
       <c r="B46" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>135615655</v>
       </c>
       <c r="B50" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135615652</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135615634</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135615637</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135615643</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135615653</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135615659</v>
       </c>
       <c r="B7" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135615625</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135615626</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135615627</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135615628</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135615629</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135615636</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135615641</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135615642</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135615644</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135615646</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135615649</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135615658</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135615660</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135615664</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135615665</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135615666</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135615667</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135615670</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135615671</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135615672</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135615674</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135615675</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135615631</v>
       </c>
       <c r="B31" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135615640</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135615663</v>
       </c>
       <c r="B33" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135615632</v>
       </c>
       <c r="B34" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135615635</v>
       </c>
       <c r="B35" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135615639</v>
       </c>
       <c r="B36" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135615645</v>
       </c>
       <c r="B37" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135615647</v>
       </c>
       <c r="B38" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135615648</v>
       </c>
       <c r="B39" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135615654</v>
       </c>
       <c r="B40" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135615656</v>
       </c>
       <c r="B41" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135615657</v>
       </c>
       <c r="B42" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135615661</v>
       </c>
       <c r="B43" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135615662</v>
       </c>
       <c r="B44" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135615668</v>
       </c>
       <c r="B45" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135615673</v>
       </c>
       <c r="B46" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135615651</v>
       </c>
       <c r="B47" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135615669</v>
       </c>
       <c r="B48" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135615650</v>
       </c>
       <c r="B49" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>135615655</v>
       </c>
       <c r="B50" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135615652</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135615634</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135615637</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135615643</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135615653</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135615659</v>
       </c>
       <c r="B7" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135615625</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135615626</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135615627</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135615628</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135615629</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135615636</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135615641</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135615642</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135615644</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135615646</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135615649</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135615658</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135615660</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135615664</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135615665</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135615666</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135615667</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135615670</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135615671</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135615672</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135615674</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135615675</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135615631</v>
       </c>
       <c r="B31" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135615640</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135615663</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135615632</v>
       </c>
       <c r="B34" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135615635</v>
       </c>
       <c r="B35" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135615639</v>
       </c>
       <c r="B36" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135615645</v>
       </c>
       <c r="B37" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135615647</v>
       </c>
       <c r="B38" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135615648</v>
       </c>
       <c r="B39" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135615654</v>
       </c>
       <c r="B40" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135615656</v>
       </c>
       <c r="B41" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135615657</v>
       </c>
       <c r="B42" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135615661</v>
       </c>
       <c r="B43" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135615662</v>
       </c>
       <c r="B44" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135615668</v>
       </c>
       <c r="B45" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135615673</v>
       </c>
       <c r="B46" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>135615655</v>
       </c>
       <c r="B50" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27839-2026 artfynd.xlsx
+++ b/artfynd/A 27839-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135615652</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135615634</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135615637</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135615643</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135615653</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135615659</v>
       </c>
       <c r="B7" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135615633</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135615625</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135615626</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135615627</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135615628</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135615629</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135615636</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135615641</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135615642</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135615644</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135615646</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135615649</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135615658</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135615660</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135615664</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135615665</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135615666</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135615667</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135615670</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135615671</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135615672</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135615674</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135615675</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135615631</v>
       </c>
       <c r="B31" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135615640</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135615663</v>
       </c>
       <c r="B33" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135615632</v>
       </c>
       <c r="B34" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135615635</v>
       </c>
       <c r="B35" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135615639</v>
       </c>
       <c r="B36" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135615645</v>
       </c>
       <c r="B37" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135615647</v>
       </c>
       <c r="B38" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135615648</v>
       </c>
       <c r="B39" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135615654</v>
       </c>
       <c r="B40" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135615656</v>
       </c>
       <c r="B41" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135615657</v>
       </c>
       <c r="B42" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135615661</v>
       </c>
       <c r="B43" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135615662</v>
       </c>
       <c r="B44" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135615668</v>
       </c>
       <c r="B45" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135615673</v>
       </c>
       <c r="B46" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135615651</v>
       </c>
       <c r="B47" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135615669</v>
       </c>
       <c r="B48" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>135615655</v>
       </c>
       <c r="B50" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
